--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -704,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -750,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -796,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -842,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -888,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -934,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -980,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1026,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1072,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1118,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1164,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1210,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1256,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1302,7 +1167,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1348,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-29</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1394,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1440,7 +1305,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1486,7 +1351,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-23</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1532,7 +1397,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-05</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1578,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1624,7 +1489,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1670,7 +1535,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1716,7 +1581,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1762,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1808,7 +1673,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1854,7 +1719,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1900,7 +1765,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1946,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1992,7 +1857,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2038,7 +1903,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2084,7 +1949,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2130,7 +1995,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2176,7 +2041,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2222,7 +2087,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2268,7 +2133,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2314,7 +2179,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2360,7 +2225,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2406,7 +2271,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2452,7 +2317,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2498,7 +2363,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2544,7 +2409,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2590,7 +2455,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2636,7 +2501,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2682,7 +2547,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2728,7 +2593,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2774,7 +2639,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2820,7 +2685,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2866,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2912,7 +2777,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2958,7 +2823,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4154,7 +4019,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4200,7 +4065,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4222,1213 +4087,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>大学阁 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3160呎 (4+房)
-$25,805万
-$81,663/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1507呎 (4+房)
-$9,522万
-$63,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1505呎 (4+房)
-$9,187万
-$61,045/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (4+房)
-$8,200万
-$54,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-$7,900万
-$52,457/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (3房)
-$8,633万
-$57,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-$8,100万
-$53,785/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1584呎 (4+房)
-$8,080万
-$51,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$7,680万
-$50,928/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1547呎 (4+房)
-$8,010万
-$51,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$7,730万
-$51,259/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1547呎 (4+房)
-$7,300万
-$47,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$6,600万
-$43,767/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$6,500万
-$43,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1547呎 (4+房)
-$6,880万
-$44,473/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$7,180万
-$47,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$6,950万
-$46,088/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,600万
-$43,767/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,000万
-$39,788/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,800万
-$45,093/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,500万
-$43,103/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,368万
-$42,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$5,880万
-$38,992/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1475呎 (3房)
-$6,800万
-$46,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1438呎 (3房)
-$6,500万
-$45,202/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>大学阁 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3154呎 (4+房)
-$25,430万
-$80,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1507呎 (4+房)
-$8,388万
-$55,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1505呎 (4+房)
-$8,041万
-$53,427/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (4+房)
-$7,950万
-$52,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-$7,800万
-$51,793/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (4+房)
-$7,600万
-$50,465/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-$7,400万
-$49,137/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$6,950万
-$46,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$6,880万
-$45,623/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$7,398万
-$49,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$7,200万
-$47,745/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$6,750万
-$44,761/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1584呎 (4+房)
-$6,600万
-$41,667/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-$6,500万
-$43,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-$6,850万
-$45,424/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,340万
-$42,042/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,260万
-$41,512/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,250万
-$41,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,180万
-$40,981/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,120万
-$40,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,480万
-$42,971/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-$6,280万
-$41,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-$6,200万
-$41,114/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (3房)
-$6,580万
-$45,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1438呎 (3房)
-$6,450万
-$44,854/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>大学阁 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>23 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 3237呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1507呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1505呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1547呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1506呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1506呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1584呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1584呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1584呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1584呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1584呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1508呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1508呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (3房)
-$6,450万
-$44,854/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1438呎 (3房)
-$6,400万
-$44,506/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +138,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4087,4 +4259,1213 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3160呎 (4+房)
+$25805万
+$81,663/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1507呎 (4+房)
+$9522万
+$63,185/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1505呎 (4+房)
+$9187万
+$61,045/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1506呎 (4+房)
+$8200万
+$54,449/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+$7900万
+$52,457/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1506呎 (3房)
+$8633万
+$57,324/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+$8100万
+$53,785/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+$8080万
+$51,010/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$7680万
+$50,928/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1547呎 (4+房)
+$8010万
+$51,778/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$7730万
+$51,259/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1547呎 (4+房)
+$7300万
+$47,188/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$6600万
+$43,767/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$6500万
+$43,103/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1547呎 (4+房)
+$6880万
+$44,473/呎
+(22年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$7180万
+$47,613/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$6950万
+$46,088/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6600万
+$43,767/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6000万
+$39,788/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6800万
+$45,093/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6500万
+$43,103/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6368万
+$42,228/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$5880万
+$38,992/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1475呎 (3房)
+$6800万
+$46,102/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1438呎 (3房)
+$6500万
+$45,202/呎
+(23年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3154呎 (4+房)
+$25430万
+$80,628/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1507呎 (4+房)
+$8388万
+$55,660/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1505呎 (4+房)
+$8041万
+$53,427/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1506呎 (4+房)
+$7950万
+$52,789/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+$7800万
+$51,793/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1506呎 (4+房)
+$7600万
+$50,465/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+$7400万
+$49,137/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$6950万
+$46,088/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$6880万
+$45,623/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$7398万
+$49,058/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$7200万
+$47,745/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$6750万
+$44,761/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+$6600万
+$41,667/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+$6500万
+$43,103/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+$6850万
+$45,424/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6340万
+$42,042/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6260万
+$41,512/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6250万
+$41,446/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6180万
+$40,981/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6120万
+$40,584/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6480万
+$42,971/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+$6280万
+$41,645/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+$6200万
+$41,114/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (3房)
+$6580万
+$45,758/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1438呎 (3房)
+$6450万
+$44,854/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 3237呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1507呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1505呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1547呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1506呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1506呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1584呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1584呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1508呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1508呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (3房)
+$6450万
+$44,854/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1438呎 (3房)
+$6400万
+$44,506/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -706,6 +710,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -752,6 +776,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -798,6 +842,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -844,6 +908,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -890,6 +974,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -936,6 +1040,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -982,6 +1106,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1028,6 +1172,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1074,6 +1238,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1120,6 +1304,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1166,6 +1370,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1212,6 +1436,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1258,6 +1502,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1304,6 +1568,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1350,6 +1634,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1396,6 +1700,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1442,6 +1766,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1488,6 +1832,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1534,6 +1898,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1580,6 +1964,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1626,6 +2030,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1672,6 +2096,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1718,6 +2162,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1764,6 +2228,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1810,6 +2294,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1856,6 +2360,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1902,6 +2426,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1948,6 +2492,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1994,6 +2558,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2040,6 +2624,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2086,6 +2690,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2132,6 +2756,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2178,6 +2822,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2224,6 +2888,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2270,6 +2954,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2316,6 +3020,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2362,6 +3086,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2408,6 +3152,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2454,6 +3218,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2500,6 +3284,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2546,6 +3350,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2592,6 +3416,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2638,6 +3482,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2684,6 +3548,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2730,6 +3614,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2776,6 +3680,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2822,6 +3746,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2868,6 +3812,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2914,6 +3878,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2960,6 +3944,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3006,6 +4010,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3056,6 +4080,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3106,6 +4150,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3156,6 +4220,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3206,6 +4290,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3256,6 +4360,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3306,6 +4430,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3356,6 +4500,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3406,6 +4570,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3456,6 +4640,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3506,6 +4710,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3556,6 +4780,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3606,6 +4850,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3656,6 +4920,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3706,6 +4990,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3756,6 +5060,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3806,6 +5130,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3856,6 +5200,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3906,6 +5270,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3956,6 +5340,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4006,6 +5410,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4056,6 +5480,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4106,6 +5550,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4156,6 +5620,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4202,6 +5686,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4248,13 +5752,33 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4374,7 +5898,7 @@
           <t>A | 3160呎 (4+房)
 $25805万
 $81,663/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -4390,7 +5914,7 @@
           <t>A | 1507呎 (4+房)
 $9522万
 $63,185/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -4398,7 +5922,7 @@
           <t>B | 1505呎 (4+房)
 $9187万
 $61,045/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +5937,7 @@
           <t>A | 1506呎 (4+房)
 $8200万
 $54,449/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -4421,7 +5945,7 @@
           <t>B | 1506呎 (4+房)
 $7900万
 $52,457/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -4436,7 +5960,7 @@
           <t>A | 1506呎 (3房)
 $8633万
 $57,324/呎
-(23年-02月)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -4444,7 +5968,7 @@
           <t>B | 1506呎 (4+房)
 $8100万
 $53,785/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -4459,7 +5983,7 @@
           <t>A | 1584呎 (4+房)
 $8080万
 $51,010/呎
-(23年-02月)</t>
+(23年-02月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -4467,7 +5991,7 @@
           <t>B | 1508呎 (4+房)
 $7680万
 $50,928/呎
-(23年-02月)</t>
+(23年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -4482,7 +6006,7 @@
           <t>A | 1547呎 (4+房)
 $8010万
 $51,778/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -4490,7 +6014,7 @@
           <t>B | 1508呎 (4+房)
 $7730万
 $51,259/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -4505,7 +6029,7 @@
           <t>A | 1547呎 (4+房)
 $7300万
 $47,188/呎
-(22年-12月)</t>
+(22年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -4513,7 +6037,7 @@
           <t>B | 1508呎 (4+房)
 $6600万
 $43,767/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -4528,7 +6052,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(22年-12月)</t>
+(22年-12月-29日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -4536,7 +6060,7 @@
           <t>B | 1547呎 (4+房)
 $6880万
 $44,473/呎
-(22年-12月)</t>
+(22年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -4551,7 +6075,7 @@
           <t>A | 1508呎 (4+房)
 $7180万
 $47,613/呎
-(22年-07月)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -4559,7 +6083,7 @@
           <t>B | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -4574,7 +6098,7 @@
           <t>A | 1508呎 (3房)
 $6600万
 $43,767/呎
-(23年-01月)</t>
+(23年-01月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -4582,7 +6106,7 @@
           <t>B | 1508呎 (3房)
 $6000万
 $39,788/呎
-(22年-10月)</t>
+(22年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -4597,7 +6121,7 @@
           <t>A | 1508呎 (3房)
 $6800万
 $45,093/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -4605,7 +6129,7 @@
           <t>B | 1508呎 (3房)
 $6500万
 $43,103/呎
-(22年-05月)</t>
+(22年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -4620,7 +6144,7 @@
           <t>A | 1508呎 (3房)
 $6368万
 $42,228/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -4628,7 +6152,7 @@
           <t>B | 1508呎 (3房)
 $5880万
 $38,992/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -4643,7 +6167,7 @@
           <t>A | 1475呎 (3房)
 $6800万
 $46,102/呎
-(23年-02月)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -4651,7 +6175,7 @@
           <t>B | 1438呎 (3房)
 $6500万
 $45,202/呎
-(23年-01月)</t>
+(23年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -4777,7 +6301,7 @@
           <t>A | 3154呎 (4+房)
 $25430万
 $80,628/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -4793,7 +6317,7 @@
           <t>A | 1507呎 (4+房)
 $8388万
 $55,660/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -4801,7 +6325,7 @@
           <t>B | 1505呎 (4+房)
 $8041万
 $53,427/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -4816,7 +6340,7 @@
           <t>A | 1506呎 (4+房)
 $7950万
 $52,789/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -4824,7 +6348,7 @@
           <t>B | 1506呎 (4+房)
 $7800万
 $51,793/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -4839,7 +6363,7 @@
           <t>A | 1506呎 (4+房)
 $7600万
 $50,465/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -4847,7 +6371,7 @@
           <t>B | 1506呎 (4+房)
 $7400万
 $49,137/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -4862,7 +6386,7 @@
           <t>A | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -4870,7 +6394,7 @@
           <t>B | 1508呎 (4+房)
 $6880万
 $45,623/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -4885,7 +6409,7 @@
           <t>A | 1508呎 (4+房)
 $7398万
 $49,058/呎
-(24年-01月)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -4893,7 +6417,7 @@
           <t>B | 1508呎 (4+房)
 $7200万
 $47,745/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -4908,7 +6432,7 @@
           <t>A | 1508呎 (4+房)
 $6750万
 $44,761/呎
-(24年-01月)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -4916,7 +6440,7 @@
           <t>B | 1584呎 (4+房)
 $6600万
 $41,667/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -4931,7 +6455,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -4939,7 +6463,7 @@
           <t>B | 1508呎 (4+房)
 $6850万
 $45,424/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -4954,7 +6478,7 @@
           <t>A | 1508呎 (3房)
 $6340万
 $42,042/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -4962,7 +6486,7 @@
           <t>B | 1508呎 (3房)
 $6260万
 $41,512/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -4977,7 +6501,7 @@
           <t>A | 1508呎 (3房)
 $6250万
 $41,446/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -4985,7 +6509,7 @@
           <t>B | 1508呎 (3房)
 $6180万
 $40,981/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -5000,7 +6524,7 @@
           <t>A | 1508呎 (3房)
 $6120万
 $40,584/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -5008,7 +6532,7 @@
           <t>B | 1508呎 (3房)
 $6480万
 $42,971/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -5023,7 +6547,7 @@
           <t>A | 1508呎 (3房)
 $6280万
 $41,645/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -5031,7 +6555,7 @@
           <t>B | 1508呎 (3房)
 $6200万
 $41,114/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -5046,7 +6570,7 @@
           <t>A | 1438呎 (3房)
 $6580万
 $45,758/呎
-(23年-12月)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -5054,7 +6578,7 @@
           <t>B | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -5449,7 +6973,7 @@
           <t>A | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -5457,7 +6981,7 @@
           <t>B | 1438呎 (3房)
 $6400万
 $44,506/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -5898,7 +5898,7 @@
           <t>A | 3160呎 (4+房)
 $25805万
 $81,663/呎
-(22年-01月-18日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
           <t>A | 1507呎 (4+房)
 $9522万
 $63,185/呎
-(22年-01月-18日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -5922,7 +5922,7 @@
           <t>B | 1505呎 (4+房)
 $9187万
 $61,045/呎
-(22年-01月-18日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
           <t>A | 1506呎 (4+房)
 $8200万
 $54,449/呎
-(23年-07月-05日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5945,7 +5945,7 @@
           <t>B | 1506呎 (4+房)
 $7900万
 $52,457/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
           <t>A | 1506呎 (3房)
 $8633万
 $57,324/呎
-(23年-02月-23日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5968,7 +5968,7 @@
           <t>B | 1506呎 (4+房)
 $8100万
 $53,785/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
           <t>A | 1584呎 (4+房)
 $8080万
 $51,010/呎
-(23年-02月-27日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5991,7 +5991,7 @@
           <t>B | 1508呎 (4+房)
 $7680万
 $50,928/呎
-(23年-02月-05日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
           <t>A | 1547呎 (4+房)
 $8010万
 $51,778/呎
-(21年-11月-09日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6014,7 +6014,7 @@
           <t>B | 1508呎 (4+房)
 $7730万
 $51,259/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
           <t>A | 1547呎 (4+房)
 $7300万
 $47,188/呎
-(22年-12月-04日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6037,7 +6037,7 @@
           <t>B | 1508呎 (4+房)
 $6600万
 $43,767/呎
-(23年-07月-24日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(22年-12月-29日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6060,7 +6060,7 @@
           <t>B | 1547呎 (4+房)
 $6880万
 $44,473/呎
-(22年-12月-06日)</t>
+(22年-12月)</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
           <t>A | 1508呎 (4+房)
 $7180万
 $47,613/呎
-(22年-07月-13日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6083,7 +6083,7 @@
           <t>B | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(22年-02月-16日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
           <t>A | 1508呎 (3房)
 $6600万
 $43,767/呎
-(23年-01月-05日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6106,7 +6106,7 @@
           <t>B | 1508呎 (3房)
 $6000万
 $39,788/呎
-(22年-10月-23日)</t>
+(22年-10月)</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
           <t>A | 1508呎 (3房)
 $6800万
 $45,093/呎
-(22年-05月-02日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6129,7 +6129,7 @@
           <t>B | 1508呎 (3房)
 $6500万
 $43,103/呎
-(22年-05月-15日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
           <t>A | 1508呎 (3房)
 $6368万
 $42,228/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6152,7 +6152,7 @@
           <t>B | 1508呎 (3房)
 $5880万
 $38,992/呎
-(22年-05月-02日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
           <t>A | 1475呎 (3房)
 $6800万
 $46,102/呎
-(23年-02月-15日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6175,7 +6175,7 @@
           <t>B | 1438呎 (3房)
 $6500万
 $45,202/呎
-(23年-01月-16日)</t>
+(23年-01月)</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
           <t>A | 3154呎 (4+房)
 $25430万
 $80,628/呎
-(23年-11月-21日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
           <t>A | 1507呎 (4+房)
 $8388万
 $55,660/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6325,7 +6325,7 @@
           <t>B | 1505呎 (4+房)
 $8041万
 $53,427/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
           <t>A | 1506呎 (4+房)
 $7950万
 $52,789/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>B | 1506呎 (4+房)
 $7800万
 $51,793/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
           <t>A | 1506呎 (4+房)
 $7600万
 $50,465/呎
-(24年-08月-20日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6371,7 +6371,7 @@
           <t>B | 1506呎 (4+房)
 $7400万
 $49,137/呎
-(25年-03月-11日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
           <t>A | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>B | 1508呎 (4+房)
 $6880万
 $45,623/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
           <t>A | 1508呎 (4+房)
 $7398万
 $49,058/呎
-(24年-01月-02日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6417,7 +6417,7 @@
           <t>B | 1508呎 (4+房)
 $7200万
 $47,745/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
           <t>A | 1508呎 (4+房)
 $6750万
 $44,761/呎
-(24年-01月-02日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6440,7 +6440,7 @@
           <t>B | 1584呎 (4+房)
 $6600万
 $41,667/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6463,7 +6463,7 @@
           <t>B | 1508呎 (4+房)
 $6850万
 $45,424/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
           <t>A | 1508呎 (3房)
 $6340万
 $42,042/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6486,7 +6486,7 @@
           <t>B | 1508呎 (3房)
 $6260万
 $41,512/呎
-(24年-12月-15日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
           <t>A | 1508呎 (3房)
 $6250万
 $41,446/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>B | 1508呎 (3房)
 $6180万
 $40,981/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
           <t>A | 1508呎 (3房)
 $6120万
 $40,584/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6532,7 +6532,7 @@
           <t>B | 1508呎 (3房)
 $6480万
 $42,971/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
           <t>A | 1508呎 (3房)
 $6280万
 $41,645/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6555,7 +6555,7 @@
           <t>B | 1508呎 (3房)
 $6200万
 $41,114/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
           <t>A | 1438呎 (3房)
 $6580万
 $45,758/呎
-(23年-12月-12日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
           <t>A | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-08月-11日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6981,7 +6981,7 @@
           <t>B | 1438呎 (3房)
 $6400万
 $44,506/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-大学阁.xlsx
+++ b/files/港岛-半山区西部-大学阁.xlsx
@@ -5898,7 +5898,7 @@
           <t>A | 3160呎 (4+房)
 $25805万
 $81,663/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5914,7 +5914,7 @@
           <t>A | 1507呎 (4+房)
 $9522万
 $63,185/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -5922,7 +5922,7 @@
           <t>B | 1505呎 (4+房)
 $9187万
 $61,045/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
           <t>A | 1506呎 (4+房)
 $8200万
 $54,449/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5945,7 +5945,7 @@
           <t>B | 1506呎 (4+房)
 $7900万
 $52,457/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
           <t>A | 1506呎 (3房)
 $8633万
 $57,324/呎
-(23年-02月)</t>
+(23年-02月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5968,7 +5968,7 @@
           <t>B | 1506呎 (4+房)
 $8100万
 $53,785/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
           <t>A | 1584呎 (4+房)
 $8080万
 $51,010/呎
-(23年-02月)</t>
+(23年-02月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5991,7 +5991,7 @@
           <t>B | 1508呎 (4+房)
 $7680万
 $50,928/呎
-(23年-02月)</t>
+(23年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
           <t>A | 1547呎 (4+房)
 $8010万
 $51,778/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6014,7 +6014,7 @@
           <t>B | 1508呎 (4+房)
 $7730万
 $51,259/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
           <t>A | 1547呎 (4+房)
 $7300万
 $47,188/呎
-(22年-12月)</t>
+(22年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6037,7 +6037,7 @@
           <t>B | 1508呎 (4+房)
 $6600万
 $43,767/呎
-(23年-07月)</t>
+(23年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(22年-12月)</t>
+(22年-12月-29日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6060,7 +6060,7 @@
           <t>B | 1547呎 (4+房)
 $6880万
 $44,473/呎
-(22年-12月)</t>
+(22年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
           <t>A | 1508呎 (4+房)
 $7180万
 $47,613/呎
-(22年-07月)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6083,7 +6083,7 @@
           <t>B | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
           <t>A | 1508呎 (3房)
 $6600万
 $43,767/呎
-(23年-01月)</t>
+(23年-01月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6106,7 +6106,7 @@
           <t>B | 1508呎 (3房)
 $6000万
 $39,788/呎
-(22年-10月)</t>
+(22年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
           <t>A | 1508呎 (3房)
 $6800万
 $45,093/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6129,7 +6129,7 @@
           <t>B | 1508呎 (3房)
 $6500万
 $43,103/呎
-(22年-05月)</t>
+(22年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
           <t>A | 1508呎 (3房)
 $6368万
 $42,228/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6152,7 +6152,7 @@
           <t>B | 1508呎 (3房)
 $5880万
 $38,992/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
           <t>A | 1475呎 (3房)
 $6800万
 $46,102/呎
-(23年-02月)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6175,7 +6175,7 @@
           <t>B | 1438呎 (3房)
 $6500万
 $45,202/呎
-(23年-01月)</t>
+(23年-01月-16日)</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
           <t>A | 3154呎 (4+房)
 $25430万
 $80,628/呎
-(23年-11月)</t>
+(23年-11月-21日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
           <t>A | 1507呎 (4+房)
 $8388万
 $55,660/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6325,7 +6325,7 @@
           <t>B | 1505呎 (4+房)
 $8041万
 $53,427/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
           <t>A | 1506呎 (4+房)
 $7950万
 $52,789/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>B | 1506呎 (4+房)
 $7800万
 $51,793/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
           <t>A | 1506呎 (4+房)
 $7600万
 $50,465/呎
-(24年-08月)</t>
+(24年-08月-20日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6371,7 +6371,7 @@
           <t>B | 1506呎 (4+房)
 $7400万
 $49,137/呎
-(25年-03月)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
           <t>A | 1508呎 (4+房)
 $6950万
 $46,088/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>B | 1508呎 (4+房)
 $6880万
 $45,623/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
           <t>A | 1508呎 (4+房)
 $7398万
 $49,058/呎
-(24年-01月)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6417,7 +6417,7 @@
           <t>B | 1508呎 (4+房)
 $7200万
 $47,745/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
           <t>A | 1508呎 (4+房)
 $6750万
 $44,761/呎
-(24年-01月)</t>
+(24年-01月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6440,7 +6440,7 @@
           <t>B | 1584呎 (4+房)
 $6600万
 $41,667/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
           <t>A | 1508呎 (4+房)
 $6500万
 $43,103/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6463,7 +6463,7 @@
           <t>B | 1508呎 (4+房)
 $6850万
 $45,424/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
           <t>A | 1508呎 (3房)
 $6340万
 $42,042/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6486,7 +6486,7 @@
           <t>B | 1508呎 (3房)
 $6260万
 $41,512/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
           <t>A | 1508呎 (3房)
 $6250万
 $41,446/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>B | 1508呎 (3房)
 $6180万
 $40,981/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
           <t>A | 1508呎 (3房)
 $6120万
 $40,584/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6532,7 +6532,7 @@
           <t>B | 1508呎 (3房)
 $6480万
 $42,971/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
           <t>A | 1508呎 (3房)
 $6280万
 $41,645/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6555,7 +6555,7 @@
           <t>B | 1508呎 (3房)
 $6200万
 $41,114/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
           <t>A | 1438呎 (3房)
 $6580万
 $45,758/呎
-(23年-12月)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
           <t>A | 1438呎 (3房)
 $6450万
 $44,854/呎
-(24年-08月)</t>
+(24年-08月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6981,7 +6981,7 @@
           <t>B | 1438呎 (3房)
 $6400万
 $44,506/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
